--- a/حركات_الشركات_منظمة/البصريات/حركات_WAB.xlsx
+++ b/حركات_الشركات_منظمة/البصريات/حركات_WAB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285D2672-11E3-4887-A9E6-72F2415B695C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB39EA04-919F-4DF1-84EC-A0EBB302C4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1874,9 +1874,6 @@
     <t>محمد عبدالرحمن محمد الورفلي</t>
   </si>
   <si>
-    <t>WAB2025105783F</t>
-  </si>
-  <si>
     <t>WAB193</t>
   </si>
   <si>
@@ -2007,6 +2004,9 @@
   </si>
   <si>
     <t>21/6/2026</t>
+  </si>
+  <si>
+    <t>WAB2025105783F1</t>
   </si>
 </sst>
 </file>
@@ -6218,13 +6218,13 @@
         <v>618</v>
       </c>
       <c r="B190" t="s">
+        <v>663</v>
+      </c>
+      <c r="C190" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="D190" s="6" t="s">
         <v>620</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>621</v>
       </c>
       <c r="E190">
         <v>500</v>
@@ -6235,16 +6235,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>621</v>
+      </c>
+      <c r="B191" t="s">
         <v>622</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="D191" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E191">
         <v>500</v>
@@ -6255,16 +6255,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>624</v>
+      </c>
+      <c r="B192" t="s">
         <v>625</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" s="6" t="s">
         <v>627</v>
-      </c>
-      <c r="D192" s="6" t="s">
-        <v>628</v>
       </c>
       <c r="E192">
         <v>500</v>
@@ -6275,16 +6275,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>628</v>
+      </c>
+      <c r="B193" t="s">
         <v>629</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="D193" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E193">
         <v>500</v>
@@ -6295,16 +6295,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>631</v>
+      </c>
+      <c r="B194" t="s">
         <v>632</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="D194" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E194">
         <v>450</v>
@@ -6315,16 +6315,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>634</v>
+      </c>
+      <c r="B195" t="s">
         <v>635</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="D195" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E195">
         <v>495</v>
@@ -6335,16 +6335,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>637</v>
+      </c>
+      <c r="B196" t="s">
         <v>638</v>
       </c>
-      <c r="B196" t="s">
+      <c r="C196" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C196" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="D196" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E196">
         <v>495</v>
@@ -6355,16 +6355,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>640</v>
+      </c>
+      <c r="B197" t="s">
         <v>641</v>
       </c>
-      <c r="B197" t="s">
+      <c r="C197" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="D197" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E197">
         <v>500</v>
@@ -6375,16 +6375,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>643</v>
+      </c>
+      <c r="B198" t="s">
         <v>644</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" s="6" t="s">
         <v>646</v>
-      </c>
-      <c r="D198" s="6" t="s">
-        <v>647</v>
       </c>
       <c r="E198">
         <v>465</v>
@@ -6395,16 +6395,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>647</v>
+      </c>
+      <c r="B199" t="s">
         <v>648</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>650</v>
-      </c>
       <c r="D199" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E199">
         <v>500</v>
@@ -6415,16 +6415,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>650</v>
+      </c>
+      <c r="B200" t="s">
         <v>651</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>653</v>
-      </c>
       <c r="D200" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E200">
         <v>435</v>
@@ -6435,16 +6435,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>653</v>
+      </c>
+      <c r="B201" t="s">
         <v>654</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>656</v>
-      </c>
       <c r="D201" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E201">
         <v>500</v>
@@ -6455,16 +6455,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>656</v>
+      </c>
+      <c r="B202" t="s">
         <v>657</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C202" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>659</v>
-      </c>
       <c r="D202" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E202">
         <v>295</v>
@@ -6475,16 +6475,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>659</v>
+      </c>
+      <c r="B203" t="s">
         <v>660</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="D203" s="6" t="s">
         <v>662</v>
-      </c>
-      <c r="D203" s="6" t="s">
-        <v>663</v>
       </c>
       <c r="E203">
         <v>500</v>
